--- a/reports/一级子公司A_利润表_2025-02.xlsx
+++ b/reports/一级子公司A_利润表_2025-02.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>150985492</v>
+        <v>153749294</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>147120487</v>
+        <v>146506344</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>293336705</v>
+        <v>293297249</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>599252</v>
+        <v>598073</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1199005</v>
+        <v>1193897</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>517974</v>
+        <v>520049</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1038991</v>
+        <v>1037853</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>439912</v>
+        <v>441552</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>879316</v>
+        <v>881278</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>402566</v>
+        <v>406752</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>807935</v>
+        <v>812178</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>219734</v>
+        <v>221165</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>438720</v>
+        <v>441940</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>175027</v>
+        <v>176849</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>350850</v>
+        <v>353700</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>148631027</v>
+        <v>151384854</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>144766022</v>
+        <v>144141904</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>74387700</v>
+        <v>74455928</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>148445420</v>
+        <v>149197871</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1367352</v>
+        <v>1361334</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>2728702</v>
+        <v>2728817</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1233626</v>
+        <v>1226526</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2467526</v>
+        <v>2457536</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>66313784</v>
+        <v>65640992</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132026207</v>
+        <v>131291087</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1404084</v>
+        <v>1401738</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2819705</v>
+        <v>2802252</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>619418</v>
+        <v>613858</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1234843</v>
+        <v>1226604</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2191437</v>
+        <v>2199306</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>4404023</v>
+        <v>4389729</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>970438</v>
+        <v>967996</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>1938981</v>
+        <v>1932170</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>3775153</v>
+        <v>3791472</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>7571110</v>
+        <v>7566520</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89852</v>
+        <v>90351</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>179836</v>
+        <v>180345</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2016550</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>4027464</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1344577</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>2687534</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>100808102</v>
+        <v>107954634</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>90013512</v>
+        <v>89918024</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>88169390</v>
+        <v>88072063</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>175666363</v>
+        <v>176462796</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1844122</v>
+        <v>1845961</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>3692517</v>
+        <v>3699761</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3332893</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>6679779</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1065044</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2133685</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>665280</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1331863</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>798633</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>1597419</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>599715</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1198468</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>400563</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>799878</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>334535</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>667709</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1542753</v>
+        <v>1543974</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>3080605</v>
+        <v>3081311</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1182011</v>
+        <v>1193016</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2373669</v>
+        <v>2381537</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>967384</v>
+        <v>972948</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>1931932</v>
+        <v>1943289</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>7266610</v>
+        <v>7341886</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>14567842</v>
+        <v>14676112</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349293</v>
+        <v>309370</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>697803</v>
+        <v>618934</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>668550</v>
+        <v>671769</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1336621</v>
+        <v>1345228</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>758838</v>
+        <v>671769</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1517237</v>
+        <v>1345228</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90187</v>
+        <v>89867</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>179867</v>
+        <v>180121</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>340787</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>682981</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>582373</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1166620</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>226799</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>453992</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>170183</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>340357</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>284019</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>567517</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>834741</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>1666746</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152106</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>303581</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114316</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>228143</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190830</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>380961</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133691</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>267060</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>95485</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>190899</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76313</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>152707</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>57137</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>114428</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>47822925</v>
+        <v>45569490</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>55504473</v>
+        <v>51131640</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>333143</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>667635</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94530</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>189349</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>150644</v>
+        <v>149211</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>300775</v>
+        <v>298652</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>47672281</v>
+        <v>45753422</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5325277</v>
+        <v>5282915</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>10628912</v>
+        <v>10555055</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>42347004</v>
+        <v>40470507</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>42347004</v>
+        <v>40470507</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>42347004</v>
+        <v>40470507</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>42347004</v>
+        <v>40470507</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>42347004</v>
+        <v>40470507</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
